--- a/artfynd/A 39511-2025 artfynd.xlsx
+++ b/artfynd/A 39511-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187476</v>
       </c>
       <c r="B2" t="n">
-        <v>78498</v>
+        <v>78583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187475</v>
       </c>
       <c r="B3" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130187474</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39511-2025 artfynd.xlsx
+++ b/artfynd/A 39511-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187476</v>
       </c>
       <c r="B2" t="n">
-        <v>78583</v>
+        <v>78586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187475</v>
+        <v>130187474</v>
       </c>
       <c r="B3" t="n">
-        <v>79799</v>
+        <v>79773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>779792</v>
+        <v>779783</v>
       </c>
       <c r="R3" t="n">
-        <v>7250842</v>
+        <v>7250860</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130187474</v>
+        <v>130187475</v>
       </c>
       <c r="B4" t="n">
-        <v>79770</v>
+        <v>79802</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>779783</v>
+        <v>779792</v>
       </c>
       <c r="R4" t="n">
-        <v>7250860</v>
+        <v>7250842</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 39511-2025 artfynd.xlsx
+++ b/artfynd/A 39511-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187476</v>
       </c>
       <c r="B2" t="n">
-        <v>78586</v>
+        <v>78612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187474</v>
       </c>
       <c r="B3" t="n">
-        <v>79773</v>
+        <v>79799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130187475</v>
       </c>
       <c r="B4" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39511-2025 artfynd.xlsx
+++ b/artfynd/A 39511-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187474</v>
+        <v>130187475</v>
       </c>
       <c r="B3" t="n">
-        <v>79799</v>
+        <v>79828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>779783</v>
+        <v>779792</v>
       </c>
       <c r="R3" t="n">
-        <v>7250860</v>
+        <v>7250842</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130187475</v>
+        <v>130187474</v>
       </c>
       <c r="B4" t="n">
-        <v>79828</v>
+        <v>79799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>779792</v>
+        <v>779783</v>
       </c>
       <c r="R4" t="n">
-        <v>7250842</v>
+        <v>7250860</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 39511-2025 artfynd.xlsx
+++ b/artfynd/A 39511-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187476</v>
       </c>
       <c r="B2" t="n">
-        <v>78612</v>
+        <v>78614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187475</v>
+        <v>130187474</v>
       </c>
       <c r="B3" t="n">
-        <v>79828</v>
+        <v>79801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>779792</v>
+        <v>779783</v>
       </c>
       <c r="R3" t="n">
-        <v>7250842</v>
+        <v>7250860</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130187474</v>
+        <v>130187475</v>
       </c>
       <c r="B4" t="n">
-        <v>79799</v>
+        <v>79830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>779783</v>
+        <v>779792</v>
       </c>
       <c r="R4" t="n">
-        <v>7250860</v>
+        <v>7250842</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 39511-2025 artfynd.xlsx
+++ b/artfynd/A 39511-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187474</v>
+        <v>130187475</v>
       </c>
       <c r="B3" t="n">
-        <v>79801</v>
+        <v>79830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>779783</v>
+        <v>779792</v>
       </c>
       <c r="R3" t="n">
-        <v>7250860</v>
+        <v>7250842</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130187475</v>
+        <v>130187474</v>
       </c>
       <c r="B4" t="n">
-        <v>79830</v>
+        <v>79801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>779792</v>
+        <v>779783</v>
       </c>
       <c r="R4" t="n">
-        <v>7250842</v>
+        <v>7250860</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 39511-2025 artfynd.xlsx
+++ b/artfynd/A 39511-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130187476</v>
       </c>
       <c r="B2" t="n">
-        <v>78614</v>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187475</v>
+        <v>130187470</v>
       </c>
       <c r="B3" t="n">
-        <v>79830</v>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>779792</v>
+        <v>779793</v>
       </c>
       <c r="R3" t="n">
-        <v>7250842</v>
+        <v>7250976</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130187474</v>
+        <v>130187475</v>
       </c>
       <c r="B4" t="n">
-        <v>79801</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>779783</v>
+        <v>779792</v>
       </c>
       <c r="R4" t="n">
-        <v>7250860</v>
+        <v>7250842</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,6 +1008,118 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130187474</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Boden-Skellefteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>779783</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7250860</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39511-2025 artfynd.xlsx
+++ b/artfynd/A 39511-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187476</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187470</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187475</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,8 +1140,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187474</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>